--- a/進捗/TODo.xlsx
+++ b/進捗/TODo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118550CA-8C99-4301-8419-CDD13DA8422D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5103BA-49A8-4308-8B5B-F0505D24CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>まず気になったところ</t>
     <rPh sb="2" eb="3">
@@ -159,6 +159,27 @@
     <t>そのあと、ファイル分けかな</t>
     <rPh sb="9" eb="10">
       <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionManagerをweak_ptrにする→衝撃波などは親がもつようにする</t>
+    <rPh sb="29" eb="32">
+      <t>ショウゲキハ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>オヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Player.hをきれいにしたっていい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はPlayerをCapsuleColliderにする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -485,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J13"/>
+  <dimension ref="A2:J18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:10">
@@ -549,6 +570,21 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/進捗/TODo.xlsx
+++ b/進捗/TODo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5103BA-49A8-4308-8B5B-F0505D24CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC6D591-4241-4FD5-BCC6-81B05681A2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>まず気になったところ</t>
     <rPh sb="2" eb="3">
@@ -180,6 +180,39 @@
     <t>次はPlayerをCapsuleColliderにする</t>
     <rPh sb="0" eb="1">
       <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerの上方向の移動値によって上昇するようにする</t>
+    <rPh sb="7" eb="10">
+      <t>ウエホウコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他にあったらそっち優先する</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ユウセン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -506,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J18"/>
+  <dimension ref="A2:J21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:10">
@@ -580,9 +613,22 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
